--- a/reports/scan/sqlite_devops_sqlite.xlsx
+++ b/reports/scan/sqlite_devops_sqlite.xlsx
@@ -46,12 +46,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -490,17 +490,17 @@
           <t>20</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
         <is>
           <t>20</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E2" s="3" t="inlineStr">
+      <c r="E2" s="4" t="inlineStr">
         <is>
           <t>60</t>
         </is>
@@ -522,22 +522,22 @@
           <t>16</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C3" s="3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E3" s="3" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
+      <c r="F3" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -549,17 +549,17 @@
           <t>deployments</t>
         </is>
       </c>
-      <c r="B4" s="4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C4" s="4" t="inlineStr">
+      <c r="C4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="D4" s="4" t="inlineStr">
+      <c r="D4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -569,7 +569,7 @@
           <t>27</t>
         </is>
       </c>
-      <c r="F4" s="4" t="inlineStr">
+      <c r="F4" s="3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -601,7 +601,7 @@
           <t>36</t>
         </is>
       </c>
-      <c r="F5" s="4" t="inlineStr">
+      <c r="F5" s="3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -628,7 +628,7 @@
           <t>4</t>
         </is>
       </c>
-      <c r="E6" s="4" t="inlineStr">
+      <c r="E6" s="3" t="inlineStr">
         <is>
           <t>9</t>
         </is>

--- a/reports/scan/sqlite_devops_sqlite.xlsx
+++ b/reports/scan/sqlite_devops_sqlite.xlsx
@@ -41,12 +41,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCC99"/>
+        <fgColor rgb="00FFEB9C"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFEB9C"/>
+        <fgColor rgb="00FFCC99"/>
       </patternFill>
     </fill>
     <fill>
@@ -487,27 +487,27 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="C2" s="3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>48</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -519,27 +519,27 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="C3" s="3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>48</t>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D3" s="3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E3" s="3" t="inlineStr">
+        <is>
+          <t>45</t>
         </is>
       </c>
       <c r="F3" s="3" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -549,27 +549,27 @@
           <t>deployments</t>
         </is>
       </c>
-      <c r="B4" s="3" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="C4" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="3" t="inlineStr">
         <is>
           <t>27</t>
         </is>
       </c>
-      <c r="F4" s="3" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>12</t>
         </is>
@@ -583,25 +583,25 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D5" s="3" t="inlineStr">
+        <is>
           <t>16</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="3" t="inlineStr">
         <is>
           <t>36</t>
         </is>
       </c>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>16</t>
         </is>
@@ -615,20 +615,20 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="E6" s="3" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -734,7 +734,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10">
@@ -744,7 +744,7 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11">

--- a/reports/scan/sqlite_devops_sqlite.xlsx
+++ b/reports/scan/sqlite_devops_sqlite.xlsx
@@ -32,7 +32,7 @@
       <b val="1"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,11 +47,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFCC99"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -72,13 +67,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -500,9 +494,9 @@
           <t>16</t>
         </is>
       </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>48</t>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>36</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -549,12 +543,12 @@
           <t>deployments</t>
         </is>
       </c>
-      <c r="B4" s="5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -581,9 +575,9 @@
           <t>audit_log</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>16</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -613,17 +607,17 @@
           <t>public_metrics</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
+      <c r="B6" s="4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C6" s="4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="D6" s="5" t="inlineStr">
+      <c r="D6" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -633,7 +627,7 @@
           <t>9</t>
         </is>
       </c>
-      <c r="F6" s="5" t="inlineStr">
+      <c r="F6" s="4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
